--- a/excel_reports/backtest_compare/s15/compare_s15_M15_20260528_0800_20260608_1000.xlsx
+++ b/excel_reports/backtest_compare/s15/compare_s15_M15_20260528_0800_20260608_1000.xlsx
@@ -514,7 +514,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-09 15:10:29</t>
+          <t>2026-06-18 17:05:19</t>
         </is>
       </c>
     </row>
@@ -1178,10 +1178,10 @@
         </is>
       </c>
       <c r="D2" s="9" t="n">
-        <v>46178.12427083333</v>
+        <v>46178.1659375</v>
       </c>
       <c r="E2" s="9" t="n">
-        <v>46178.25159722222</v>
+        <v>46178.29326388889</v>
       </c>
       <c r="F2" s="8" t="n">
         <v>4475.5225</v>
@@ -1264,14 +1264,14 @@
       </c>
       <c r="AO2" s="8" t="inlineStr">
         <is>
-          <t>NEAR</t>
+          <t>LOOSE</t>
         </is>
       </c>
       <c r="AP2" s="8" t="n">
-        <v>140.07</v>
+        <v>740.0700000000001</v>
       </c>
       <c r="AQ2" s="8" t="n">
-        <v>13.95</v>
+        <v>73.95</v>
       </c>
       <c r="AR2" s="8" t="n">
         <v>0.57</v>
@@ -1317,10 +1317,10 @@
         </is>
       </c>
       <c r="D3" s="11" t="n">
-        <v>46176.03513888889</v>
+        <v>46176.07680555555</v>
       </c>
       <c r="E3" s="11" t="n">
-        <v>46176.05912037037</v>
+        <v>46176.10078703704</v>
       </c>
       <c r="F3" s="10" t="n">
         <v>4485.895</v>
@@ -1408,7 +1408,7 @@
         </is>
       </c>
       <c r="BE3" s="10" t="n">
-        <v>2394.4</v>
+        <v>2334.4</v>
       </c>
       <c r="BF3" s="10" t="n">
         <v>12.35</v>
@@ -1505,7 +1505,7 @@
       <c r="BE4" s="10" t="inlineStr"/>
       <c r="BF4" s="10" t="inlineStr"/>
       <c r="BG4" s="11" t="n">
-        <v>46176.03513888889</v>
+        <v>46176.07680555555</v>
       </c>
       <c r="BH4" s="10" t="n">
         <v>4486.34</v>
@@ -1516,7 +1516,7 @@
         </is>
       </c>
       <c r="BJ4" s="10" t="n">
-        <v>2555.6</v>
+        <v>2615.6</v>
       </c>
       <c r="BK4" s="10" t="n">
         <v>57.87</v>
@@ -1608,7 +1608,7 @@
       <c r="BE5" s="10" t="inlineStr"/>
       <c r="BF5" s="10" t="inlineStr"/>
       <c r="BG5" s="11" t="n">
-        <v>46178.12427083333</v>
+        <v>46178.1659375</v>
       </c>
       <c r="BH5" s="10" t="n">
         <v>4482.38</v>
@@ -1619,7 +1619,7 @@
         </is>
       </c>
       <c r="BJ5" s="10" t="n">
-        <v>613.95</v>
+        <v>673.95</v>
       </c>
       <c r="BK5" s="10" t="n">
         <v>8.390000000000001</v>
@@ -2312,10 +2312,10 @@
         </is>
       </c>
       <c r="D2" s="9" t="n">
-        <v>46178.12427083333</v>
+        <v>46178.1659375</v>
       </c>
       <c r="E2" s="9" t="n">
-        <v>46178.25159722222</v>
+        <v>46178.29326388889</v>
       </c>
       <c r="F2" s="8" t="n">
         <v>4475.5225</v>
@@ -2398,14 +2398,14 @@
       </c>
       <c r="AO2" s="8" t="inlineStr">
         <is>
-          <t>NEAR</t>
+          <t>LOOSE</t>
         </is>
       </c>
       <c r="AP2" s="8" t="n">
-        <v>140.07</v>
+        <v>740.0700000000001</v>
       </c>
       <c r="AQ2" s="8" t="n">
-        <v>13.95</v>
+        <v>73.95</v>
       </c>
       <c r="AR2" s="8" t="n">
         <v>0.57</v>
@@ -2848,10 +2848,10 @@
         </is>
       </c>
       <c r="D2" s="11" t="n">
-        <v>46176.03513888889</v>
+        <v>46176.07680555555</v>
       </c>
       <c r="E2" s="11" t="n">
-        <v>46176.05912037037</v>
+        <v>46176.10078703704</v>
       </c>
       <c r="F2" s="10" t="n">
         <v>4485.895</v>
@@ -2939,7 +2939,7 @@
         </is>
       </c>
       <c r="BE2" s="10" t="n">
-        <v>2394.4</v>
+        <v>2334.4</v>
       </c>
       <c r="BF2" s="10" t="n">
         <v>12.35</v>
@@ -3433,7 +3433,7 @@
       <c r="BE2" s="10" t="inlineStr"/>
       <c r="BF2" s="10" t="inlineStr"/>
       <c r="BG2" s="11" t="n">
-        <v>46176.03513888889</v>
+        <v>46176.07680555555</v>
       </c>
       <c r="BH2" s="10" t="n">
         <v>4486.34</v>
@@ -3444,7 +3444,7 @@
         </is>
       </c>
       <c r="BJ2" s="10" t="n">
-        <v>2555.6</v>
+        <v>2615.6</v>
       </c>
       <c r="BK2" s="10" t="n">
         <v>57.87</v>
@@ -3536,7 +3536,7 @@
       <c r="BE3" s="10" t="inlineStr"/>
       <c r="BF3" s="10" t="inlineStr"/>
       <c r="BG3" s="11" t="n">
-        <v>46178.12427083333</v>
+        <v>46178.1659375</v>
       </c>
       <c r="BH3" s="10" t="n">
         <v>4482.38</v>
@@ -3547,7 +3547,7 @@
         </is>
       </c>
       <c r="BJ3" s="10" t="n">
-        <v>613.95</v>
+        <v>673.95</v>
       </c>
       <c r="BK3" s="10" t="n">
         <v>8.390000000000001</v>
@@ -4372,10 +4372,10 @@
         <v>1.86</v>
       </c>
       <c r="F2" s="13" t="n">
-        <v>46176.03513888889</v>
+        <v>46176.07680555555</v>
       </c>
       <c r="G2" s="13" t="n">
-        <v>46176.03513888889</v>
+        <v>46176.07680555555</v>
       </c>
     </row>
     <row r="3">
@@ -4513,10 +4513,10 @@
         <v>1.86</v>
       </c>
       <c r="F7" s="13" t="n">
-        <v>46176.03513888889</v>
+        <v>46176.07680555555</v>
       </c>
       <c r="G7" s="13" t="n">
-        <v>46176.03513888889</v>
+        <v>46176.07680555555</v>
       </c>
     </row>
     <row r="8">
@@ -4600,10 +4600,10 @@
         <v>9.460000000000001</v>
       </c>
       <c r="F10" s="13" t="n">
-        <v>46178.12427083333</v>
+        <v>46178.1659375</v>
       </c>
       <c r="G10" s="13" t="n">
-        <v>46178.12427083333</v>
+        <v>46178.1659375</v>
       </c>
     </row>
     <row r="11">
@@ -4629,10 +4629,10 @@
         <v>1.86</v>
       </c>
       <c r="F11" s="13" t="n">
-        <v>46176.03513888889</v>
+        <v>46176.07680555555</v>
       </c>
       <c r="G11" s="13" t="n">
-        <v>46176.03513888889</v>
+        <v>46176.07680555555</v>
       </c>
     </row>
     <row r="12">
@@ -4658,10 +4658,10 @@
         <v>9.460000000000001</v>
       </c>
       <c r="F12" s="13" t="n">
-        <v>46178.12427083333</v>
+        <v>46178.1659375</v>
       </c>
       <c r="G12" s="13" t="n">
-        <v>46178.12427083333</v>
+        <v>46178.1659375</v>
       </c>
     </row>
     <row r="13">
@@ -4687,10 +4687,10 @@
         <v>1.86</v>
       </c>
       <c r="F13" s="13" t="n">
-        <v>46176.03513888889</v>
+        <v>46176.07680555555</v>
       </c>
       <c r="G13" s="13" t="n">
-        <v>46176.03513888889</v>
+        <v>46176.07680555555</v>
       </c>
     </row>
     <row r="14">
@@ -4774,10 +4774,10 @@
         <v>9.460000000000001</v>
       </c>
       <c r="F16" s="13" t="n">
-        <v>46178.12427083333</v>
+        <v>46178.1659375</v>
       </c>
       <c r="G16" s="13" t="n">
-        <v>46178.12427083333</v>
+        <v>46178.1659375</v>
       </c>
     </row>
     <row r="17">
@@ -4803,10 +4803,10 @@
         <v>9.460000000000001</v>
       </c>
       <c r="F17" s="13" t="n">
-        <v>46178.12427083333</v>
+        <v>46178.1659375</v>
       </c>
       <c r="G17" s="13" t="n">
-        <v>46178.12427083333</v>
+        <v>46178.1659375</v>
       </c>
     </row>
   </sheetData>
